--- a/docs/harness/wirelist/WheelSpeed-Rear-pinouts.xlsx
+++ b/docs/harness/wirelist/WheelSpeed-Rear-pinouts.xlsx
@@ -872,7 +872,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
@@ -952,7 +952,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>_TXY7m</t>
+          <t>w_ws_r_shield</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>splice I6r1ot (Sensor screen join)</t>
+          <t>splice sp_ws_r_shield (Sensor screen join)</t>
         </is>
       </c>
     </row>
